--- a/results/Int Task Remove ACC 0.3/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_1_permute.xlsx
@@ -440,597 +440,597 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.489327947046191</v>
+        <v>0.4771466939753449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4837258955829501</v>
+        <v>0.4875468562816401</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.48340983995716</v>
+        <v>0.4859093016964872</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4953047107469954</v>
+        <v>0.5275375540330905</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5291192123176124</v>
+        <v>0.5438848066954107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5319913160611464</v>
+        <v>0.5426205841922502</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5199825824366923</v>
+        <v>0.5439427732293984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5231141554275998</v>
+        <v>0.5439427732293984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5132018781157012</v>
+        <v>0.5319326594493732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5132018781157012</v>
+        <v>0.5347778501592699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.514753172977658</v>
+        <v>0.5348641098824659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5185458404871397</v>
+        <v>0.5347198836252822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5098701825669789</v>
+        <v>0.5425363947024109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5098701825669789</v>
+        <v>0.5404102650450759</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5061927580476872</v>
+        <v>0.5417607472714324</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.511566393763905</v>
+        <v>0.5434555783127875</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5022020382137474</v>
+        <v>0.5184913243420798</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5074314476727817</v>
+        <v>0.5223129751185553</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4941301983559587</v>
+        <v>0.5144412578185813</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.496340517503133</v>
+        <v>0.4964550704155372</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5128616697674162</v>
+        <v>0.4882955906789813</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5091552619811305</v>
+        <v>0.4891871711779351</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5087239633651505</v>
+        <v>0.4807123258933747</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5219113498473548</v>
+        <v>0.4863433606236095</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5248704033918703</v>
+        <v>0.4919743953538442</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5248993866588642</v>
+        <v>0.4924056939698243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5226000474773517</v>
+        <v>0.5100178592130905</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5090669320245779</v>
+        <v>0.5175445376202805</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5055054405732614</v>
+        <v>0.5129175660680472</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5216822440225463</v>
+        <v>0.5135779705088357</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5373684021662922</v>
+        <v>0.50105098846742</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.537052346540502</v>
+        <v>0.4986088031842949</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5367638940261346</v>
+        <v>0.5005051369390358</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5512727794677016</v>
+        <v>0.511997692379885</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5555823152385737</v>
+        <v>0.5127733398108635</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5600064039218501</v>
+        <v>0.5127733398108635</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.561472819216182</v>
+        <v>0.5121412285592832</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5664717426948366</v>
+        <v>0.5020550516454215</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5656098355406621</v>
+        <v>0.5296609233792833</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5861223977166706</v>
+        <v>0.5301488083736798</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6028712756501913</v>
+        <v>0.5296319401122895</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6028712756501913</v>
+        <v>0.5734222061510774</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6349888759460967</v>
+        <v>0.5567602780185382</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6361661486482757</v>
+        <v>0.5593425490921337</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6376311837870365</v>
+        <v>0.5471606059435019</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6235487664169506</v>
+        <v>0.5415012780240589</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.624583193017517</v>
+        <v>0.5490583198538139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.624583193017517</v>
+        <v>0.5658375612098996</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6248129889201111</v>
+        <v>0.5802042906276396</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5749424475126836</v>
+        <v>0.5698303512771959</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5749424475126836</v>
+        <v>0.5698303512771959</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6010563710741474</v>
+        <v>0.5600643704558378</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6010563710741474</v>
+        <v>0.5544340258033885</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5649190676773086</v>
+        <v>0.5569045042757219</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5701188037915634</v>
+        <v>0.5698620948553321</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5390915263968554</v>
+        <v>0.580863314912857</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5169420997134797</v>
+        <v>0.5803995826409553</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5223143552741265</v>
+        <v>0.5791070669485865</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5257047074346221</v>
+        <v>0.5633084261257929</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5448950805734822</v>
+        <v>0.5618178581089661</v>
       </c>
     </row>
     <row r="62">
@@ -1040,287 +1040,287 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5333445585986453</v>
+        <v>0.5578457703752367</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6593741546547127</v>
+        <v>0.5565539447606535</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6372813143497535</v>
+        <v>0.5565539447606535</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5663006034040157</v>
+        <v>0.525861355091946</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5684267330613507</v>
+        <v>0.5308595884928149</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5702933934713121</v>
+        <v>0.4945159518380912</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5729363913900375</v>
+        <v>0.4962418363797967</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5730516343802273</v>
+        <v>0.502070233356704</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5755517861973402</v>
+        <v>0.502070233356704</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5755517861973402</v>
+        <v>0.5110909301696487</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5557258514179718</v>
+        <v>0.5005493019173121</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5557258514179718</v>
+        <v>0.4967518038633315</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.521770573979099</v>
+        <v>0.5030694659902064</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5178626634794274</v>
+        <v>0.4941357189782432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4955110440048802</v>
+        <v>0.4863571621793208</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4960286023440562</v>
+        <v>0.5288059170029646</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4895349703818614</v>
+        <v>0.5277735606357549</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4952833183356428</v>
+        <v>0.5161436797155775</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4933580013139081</v>
+        <v>0.4834498644687229</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4823526407896698</v>
+        <v>0.4923511778247645</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.477898878761614</v>
+        <v>0.4962294149796565</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4937347837848283</v>
+        <v>0.4800325992745902</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4953723383699811</v>
+        <v>0.4800325992745902</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.496234935601941</v>
+        <v>0.4766698502255174</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4964074550483331</v>
+        <v>0.4964440291709681</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4937354738626138</v>
+        <v>0.4847506610945186</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4950576628997621</v>
+        <v>0.4847506610945186</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4956035144281464</v>
+        <v>0.4763634556887252</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.497787610619469</v>
+        <v>0.4765932515913194</v>
       </c>
     </row>
   </sheetData>
